--- a/artfynd/A 20262-2022 artfynd.xlsx
+++ b/artfynd/A 20262-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119500425</v>
+        <v>119500424</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487619</v>
+        <v>487641</v>
       </c>
       <c r="R2" t="n">
-        <v>6442826</v>
+        <v>6442844</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119500424</v>
+        <v>119500425</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487641</v>
+        <v>487619</v>
       </c>
       <c r="R3" t="n">
-        <v>6442844</v>
+        <v>6442826</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,50 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119679155</v>
+        <v>119500288</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norr om Vagnsjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487916</v>
+        <v>487672</v>
       </c>
       <c r="R4" t="n">
-        <v>6443010</v>
+        <v>6442776</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -949,12 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,6 +972,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119679155</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr om Vagnsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487916</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6443010</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Trehörna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20262-2022 artfynd.xlsx
+++ b/artfynd/A 20262-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119500424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119500425</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119500288</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,8 +1089,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119679155</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>